--- a/mapping/Invertebrate.xlsx
+++ b/mapping/Invertebrate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B197"/>
+  <dimension ref="A1:B200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>膀胱螺属</t>
+          <t>瓶螺属</t>
         </is>
       </c>
     </row>
@@ -2759,22 +2759,58 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ctenocephalides</t>
+          <t>Schistosoma</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>栉首蚤属</t>
+          <t>裂体吸虫属（血吸虫属）</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>Vollenhovia</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>沃伦霍维亚蚁属</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Lutzomyia</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>罗蛉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Ctenocephalides</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>栉首蚤属</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
           <t>Thrips</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>蓟马属</t>
         </is>
